--- a/Introduction To Statistics/Introduction To Statistics.xlsx
+++ b/Introduction To Statistics/Introduction To Statistics.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/macbook/Desktop/STATISTICS/Assessment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B46AF3A-54E0-A94B-A8E4-B7C0DF51A7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A9B58C-98AF-6C44-AFA2-1599C1E1821E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18980" xr2:uid="{65B5C15B-AE96-034C-AD95-96C4BD089478}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -35,40 +35,70 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
-  <si>
-    <t xml:space="preserve">Define the following terms: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is a Random Variable? What are its types? </t>
-  </si>
-  <si>
-    <t>Descriptive</t>
-  </si>
-  <si>
-    <t>E.g (Mean,Median,Mode,Graphs)</t>
-  </si>
-  <si>
-    <t>Inferntial</t>
-  </si>
-  <si>
-    <t>Used to sumarize and describe the main features of the dataset</t>
-  </si>
-  <si>
-    <t>Used to make Conclusion or predictions about a population based on a sample using tools like using Hypothesis Testing and Confidence Interval.</t>
-  </si>
-  <si>
-    <t>Q1</t>
-  </si>
-  <si>
-    <t>Q2</t>
-  </si>
-  <si>
-    <t>Population</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="41">
+  <si>
+    <t>Question 1</t>
+  </si>
+  <si>
+    <t>Given</t>
+  </si>
+  <si>
+    <t>x1</t>
+  </si>
+  <si>
+    <t>s1</t>
+  </si>
+  <si>
+    <t>n1</t>
+  </si>
+  <si>
+    <t>x2</t>
+  </si>
+  <si>
+    <t>s2</t>
+  </si>
+  <si>
+    <t>n2</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>T-STAT</t>
+  </si>
+  <si>
+    <t>DOF</t>
+  </si>
+  <si>
+    <t>T-CRIT</t>
+  </si>
+  <si>
+    <t>ALPHA</t>
+  </si>
+  <si>
+    <t>P-Value</t>
+  </si>
+  <si>
+    <t>T-Stat</t>
+  </si>
+  <si>
+    <t>t-Crit</t>
+  </si>
+  <si>
+    <t>Alpha</t>
+  </si>
+  <si>
+    <t>&gt;</t>
+  </si>
+  <si>
+    <t>&lt;</t>
+  </si>
+  <si>
+    <t>Conclusion</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Since the calculated </t>
     </r>
     <r>
       <rPr>
@@ -79,28 +109,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>entire group</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> you want to study.</t>
-    </r>
-  </si>
-  <si>
-    <t>Example: All college students in a country.</t>
-  </si>
-  <si>
-    <t>Sample</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A </t>
+      <t>t-statistic (7.018)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is </t>
     </r>
     <r>
       <rPr>
@@ -111,31 +130,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>smaller part</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of the population, used to make conclusions.</t>
-    </r>
-  </si>
-  <si>
-    <t>Example: 100 students selected from different colleges.</t>
-  </si>
-  <si>
-    <t>Q3</t>
-  </si>
-  <si>
-    <t>Mean</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The </t>
+      <t>greater</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> than the </t>
     </r>
     <r>
       <rPr>
@@ -146,31 +151,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>average</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> of a data set. Add all values and divide by how many there are.</t>
-    </r>
-  </si>
-  <si>
-    <t>Median</t>
-  </si>
-  <si>
-    <t>The middle value when the data is sorted.</t>
-  </si>
-  <si>
-    <t>Mode</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The value that occurs </t>
+      <t>t-critical value (1.974)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, and the </t>
     </r>
     <r>
       <rPr>
@@ -181,38 +172,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>most often</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> in the data.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">🔹 </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Difference:</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Mean is affected by extreme values (outliers), while </t>
+      <t>p-value (≈ 0.00000000005)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> is </t>
     </r>
     <r>
       <rPr>
@@ -223,17 +193,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>median</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is more stable. </t>
+      <t>less than the significance level (α = 0.05)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, we </t>
     </r>
     <r>
       <rPr>
@@ -244,25 +214,22 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Mode</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is useful when data repeats.</t>
-    </r>
-  </si>
-  <si>
-    <t>Q4</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">A </t>
+      <t>reject the null hypothesis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Therefore, we conclude that there is a </t>
     </r>
     <r>
       <rPr>
@@ -273,17 +240,70 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>random variable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> is a variable whose value depends on the </t>
+      <t>statistically significant difference</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> in intelligence scores between boys and girls.</t>
+    </r>
+  </si>
+  <si>
+    <t>Hypothesis</t>
+  </si>
+  <si>
+    <t>u1=u2</t>
+  </si>
+  <si>
+    <t>Null Hypo</t>
+  </si>
+  <si>
+    <t>Alternative</t>
+  </si>
+  <si>
+    <t>u1#u2</t>
+  </si>
+  <si>
+    <t>Question. 2</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Cancer</t>
+  </si>
+  <si>
+    <t>No Cancer</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Smokers</t>
+  </si>
+  <si>
+    <t>Non-Smokers</t>
+  </si>
+  <si>
+    <t>Expected Frequencies</t>
+  </si>
+  <si>
+    <t>Chi-Square</t>
+  </si>
+  <si>
+    <t>Addition</t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">So there </t>
     </r>
     <r>
       <rPr>
@@ -294,35 +314,17 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>outcome of a random event</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>.</t>
-    </r>
-  </si>
-  <si>
-    <t>Types:</t>
-  </si>
-  <si>
-    <r>
-      <t>Discrete</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Takes specific, </t>
+      <t>is a significant association</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> between </t>
     </r>
     <r>
       <rPr>
@@ -333,73 +335,25 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>countable</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> values.</t>
-    </r>
-  </si>
-  <si>
-    <t>Example: Number of books you own.</t>
-  </si>
-  <si>
-    <r>
-      <t>Continuous</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Takes </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>any value in a range</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> (can be decimal).</t>
-    </r>
-  </si>
-  <si>
-    <t>Example: Your height or weight.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What is the difference between Descriptive and Inferential Statistics? </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Define mean, median, and mode. How are they different from each other? </t>
+      <t>smoking and cancer</t>
+    </r>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>Since the P-Value is lesser then Alpha. Value So we reject Null Hypothesis.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="0.000000000000000000"/>
+    <numFmt numFmtId="169" formatCode="0.00000000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -416,28 +370,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="SymbolMT"/>
-    </font>
-    <font>
-      <i/>
+      <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -453,33 +387,57 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2"/>
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
+        <fgColor theme="9" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -488,17 +446,30 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -813,175 +784,436 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{199B9023-2AE4-5D40-B4F6-DC1076BEFB04}">
-  <dimension ref="A2:H38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <dimension ref="A2:AC41"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="58" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
+    <col min="2" max="2" width="9.5" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.83203125" customWidth="1"/>
+    <col min="8" max="8" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:8">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="A2" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B4" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10">
+        <v>89</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="E4" s="10">
+        <v>4</v>
+      </c>
+      <c r="F4" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="9"/>
+      <c r="H4" s="10">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B5" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="10">
+        <v>82</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="10">
+        <v>9</v>
+      </c>
+      <c r="F5" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="G5" s="9"/>
+      <c r="H5" s="10">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B7" s="12">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>0.99749686716300023</v>
+      </c>
+      <c r="H8" s="12">
+        <v>2</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="J8" s="3"/>
+      <c r="K8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="13"/>
+      <c r="M8" s="12">
+        <v>3</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="O8" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="P8" s="8"/>
+      <c r="Q8" s="8"/>
+      <c r="R8" s="8"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="8"/>
+      <c r="U8" s="8"/>
+      <c r="V8" s="8"/>
+      <c r="W8" s="8"/>
+      <c r="X8" s="8"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="8"/>
+      <c r="AA8" s="8"/>
+      <c r="AB8" s="8"/>
+      <c r="AC8" s="8"/>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B9" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F9">
+        <v>7.0175658996391963</v>
+      </c>
+      <c r="I9" s="3">
+        <v>7.0175658996391963</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="3">
+        <v>1.9742709570280526</v>
+      </c>
+      <c r="L9" s="13"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+      <c r="Q9" s="8"/>
+      <c r="R9" s="8"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="8"/>
+      <c r="U9" s="8"/>
+      <c r="V9" s="8"/>
+      <c r="W9" s="8"/>
+      <c r="X9" s="8"/>
+      <c r="Y9" s="8"/>
+      <c r="Z9" s="8"/>
+      <c r="AA9" s="8"/>
+      <c r="AB9" s="8"/>
+      <c r="AC9" s="8"/>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B10" s="8"/>
+      <c r="C10" s="16"/>
+      <c r="E10" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10">
+        <v>168</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="K10" s="3"/>
+      <c r="L10" s="13"/>
+      <c r="O10" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="8"/>
+      <c r="U10" s="8"/>
+      <c r="V10" s="8"/>
+      <c r="W10" s="8"/>
+      <c r="X10" s="8"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="8"/>
+      <c r="AA10" s="8"/>
+      <c r="AB10" s="8"/>
+      <c r="AC10" s="8"/>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="B11" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="F11">
+        <v>1.9742709570280526</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="3"/>
+      <c r="K11" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" s="13"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="E12" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="6">
+        <v>5.3171689273767697E-11</v>
+      </c>
+      <c r="G12" s="6"/>
+      <c r="I12" s="7">
+        <v>5.3171689273767697E-11</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="3">
+        <v>0.05</v>
+      </c>
+      <c r="L12" s="13"/>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="E13" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="F13">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A19" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5" s="7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="B8" s="1"/>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B12" s="7" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D20" s="14">
+        <v>220</v>
+      </c>
+      <c r="E20" s="14">
+        <v>230</v>
+      </c>
+      <c r="F20" s="14">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C21" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D21" s="14">
+        <v>350</v>
+      </c>
+      <c r="E21" s="14">
+        <v>640</v>
+      </c>
+      <c r="F21" s="14">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C22" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="14">
+        <v>680</v>
+      </c>
+      <c r="E22" s="14">
+        <v>910</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C26" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D26" s="3">
+        <f>(550*680)/1590</f>
+        <v>235.22012578616352</v>
+      </c>
+      <c r="E26" s="3">
+        <f>(990*680)/1590</f>
+        <v>423.39622641509436</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C27" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D27" s="3">
+        <f>(550*910)/1590</f>
+        <v>314.77987421383648</v>
+      </c>
+      <c r="E27" s="3">
+        <f>(990*910)/1590</f>
+        <v>566.60377358490564</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C30" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E30" s="15" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C31" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="D31" s="3">
+        <v>0.98481591701385918</v>
+      </c>
+      <c r="E31" s="3">
+        <v>22.833820267782531</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C32" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="3">
+        <v>3.9407133746756386</v>
+      </c>
+      <c r="E32" s="3">
+        <v>9.5075364886685705</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B35" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C35" s="1">
+        <f>D31+E31+D32+E32</f>
+        <v>37.266886048140599</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E36" s="18">
+        <f>C39</f>
+        <v>1.4093230024020717E-7</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" s="3">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B37" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="B13" s="8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="B16" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="C37" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B39" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C39" s="17">
+        <f>_xlfn.CHISQ.DIST.RT(27.71, 1)</f>
+        <v>1.4093230024020717E-7</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="E40" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F40" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="G40" s="8"/>
+      <c r="H40" s="8"/>
+      <c r="I40" s="8"/>
+    </row>
+    <row r="41" spans="2:9" x14ac:dyDescent="0.2">
+      <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C20" s="7"/>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="B24" s="7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="B30" s="7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="7"/>
-      <c r="D30" s="7"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="B32" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="2:2">
-      <c r="B34" s="9" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="35" spans="2:2">
-      <c r="B35" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="37" spans="2:2">
-      <c r="B37" s="9" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="38" spans="2:2">
-      <c r="B38" s="8" t="s">
-        <v>30</v>
-      </c>
+      <c r="C41" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="F41" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
